--- a/Master.xlsx
+++ b/Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\ipo_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927E6513-0364-4D47-802B-D19C5DD8DC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDCFCED-D9C5-45DA-B6AF-D9B38A6A8C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C55D002-01A9-4766-B153-0A6B63271353}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>uci</t>
   </si>
@@ -48,22 +48,46 @@
     <t>intraday</t>
   </si>
   <si>
-    <t>total_value</t>
-  </si>
-  <si>
     <t>bank_fund</t>
   </si>
   <si>
     <t>ipo_blocked_fund</t>
   </si>
   <si>
-    <t>broker_open_fund</t>
-  </si>
-  <si>
-    <t>broker_blocked_fund</t>
-  </si>
-  <si>
     <t>holdings_total_value</t>
+  </si>
+  <si>
+    <t>current_value</t>
+  </si>
+  <si>
+    <t>broker_withdrawable_fund</t>
+  </si>
+  <si>
+    <t>broker_investable_fund</t>
+  </si>
+  <si>
+    <t>inv-nifty</t>
+  </si>
+  <si>
+    <t>inv-gold</t>
+  </si>
+  <si>
+    <t>inv-silver</t>
+  </si>
+  <si>
+    <t>investing_amt_per_etf</t>
+  </si>
+  <si>
+    <t>etfs</t>
+  </si>
+  <si>
+    <t>day_gold</t>
+  </si>
+  <si>
+    <t>day_silver</t>
+  </si>
+  <si>
+    <t>day_nifty</t>
   </si>
 </sst>
 </file>
@@ -418,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB5-F567-4357-909C-71329154FE45}">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="11.88671875" customWidth="1"/>
@@ -426,7 +450,7 @@
     <col min="10" max="10" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,35 +473,90 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="M2">
+        <v>90</v>
+      </c>
+      <c r="N2">
+        <f>IF(P2&gt;0,1,0)+IF(R2&gt;0,1,0)+IF(T2&gt;0,1,0)+1</f>
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <f>M2/N2</f>
+        <v>90</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>IF(P2=0,0,O2/3)</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>IF(R2=0,0,O2/3)</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>IF(T2=0,0,O2/3)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDCFCED-D9C5-45DA-B6AF-D9B38A6A8C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652DA0B6-C4E8-42F0-BCA0-EA7075CDE9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C55D002-01A9-4766-B153-0A6B63271353}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>uci</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>day_nifty</t>
+  </si>
+  <si>
+    <t>zerodha_access_token</t>
   </si>
 </sst>
 </file>
@@ -442,15 +445,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB5-F567-4357-909C-71329154FE45}">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="11.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" customWidth="1"/>
-    <col min="10" max="10" width="16.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,48 +476,50 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -523,39 +528,48 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="M2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="N2">
         <v>90</v>
       </c>
-      <c r="N2">
-        <f>IF(P2&gt;0,1,0)+IF(R2&gt;0,1,0)+IF(T2&gt;0,1,0)+1</f>
+      <c r="O2">
+        <f>IF(Q2&gt;0,1,0)+IF(S2&gt;0,1,0)+IF(U2&gt;0,1,0)+1</f>
         <v>1</v>
       </c>
-      <c r="O2">
-        <f>M2/N2</f>
+      <c r="P2">
+        <f>N2/O2</f>
         <v>90</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
       <c r="Q2">
-        <f>IF(P2=0,0,O2/3)</f>
         <v>0</v>
       </c>
       <c r="R2">
+        <f>IF(Q2=0,0,P2/3)</f>
         <v>0</v>
       </c>
       <c r="S2">
-        <f>IF(R2=0,0,O2/3)</f>
         <v>0</v>
       </c>
       <c r="T2">
+        <f>IF(S2=0,0,P2/3)</f>
         <v>0</v>
       </c>
       <c r="U2">
-        <f>IF(T2=0,0,O2/3)</f>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>IF(U2=0,0,P2/3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -1,114 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652DA0B6-C4E8-42F0-BCA0-EA7075CDE9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C55D002-01A9-4766-B153-0A6B63271353}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>uci</t>
-  </si>
-  <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>mobile</t>
-  </si>
-  <si>
-    <t>communication email</t>
-  </si>
-  <si>
-    <t>account_email</t>
-  </si>
-  <si>
-    <t>intraday</t>
-  </si>
-  <si>
-    <t>bank_fund</t>
-  </si>
-  <si>
-    <t>ipo_blocked_fund</t>
-  </si>
-  <si>
-    <t>holdings_total_value</t>
-  </si>
-  <si>
-    <t>current_value</t>
-  </si>
-  <si>
-    <t>broker_withdrawable_fund</t>
-  </si>
-  <si>
-    <t>broker_investable_fund</t>
-  </si>
-  <si>
-    <t>inv-nifty</t>
-  </si>
-  <si>
-    <t>inv-gold</t>
-  </si>
-  <si>
-    <t>inv-silver</t>
-  </si>
-  <si>
-    <t>investing_amt_per_etf</t>
-  </si>
-  <si>
-    <t>etfs</t>
-  </si>
-  <si>
-    <t>day_gold</t>
-  </si>
-  <si>
-    <t>day_silver</t>
-  </si>
-  <si>
-    <t>day_nifty</t>
-  </si>
-  <si>
-    <t>zerodha_access_token</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -127,24 +46,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -444,134 +422,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB5-F567-4357-909C-71329154FE45}">
-  <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col min="9" max="9" width="11.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col width="11.88671875" customWidth="1" min="9" max="9"/>
+    <col width="10.21875" customWidth="1" min="10" max="10"/>
+    <col width="16.21875" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="43.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>communication email</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>account_email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>intraday</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>zerodha_access_token</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bank_fund</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ipo_blocked_fund</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>holdings_total_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>broker_withdrawable_fund</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>broker_investable_fund</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>still_needed_amount</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+      <c r="AE1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>90</v>
-      </c>
-      <c r="O2">
-        <f>IF(Q2&gt;0,1,0)+IF(S2&gt;0,1,0)+IF(U2&gt;0,1,0)+1</f>
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <f>N2/O2</f>
-        <v>90</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f>IF(Q2=0,0,P2/3)</f>
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <f>IF(S2=0,0,P2/3)</f>
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f>IF(U2=0,0,P2/3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -428,7 +428,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.88671875" customWidth="1" min="9" max="9"/>
     <col width="10.21875" customWidth="1" min="10" max="10"/>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -1,33 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CFrepo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Users" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>uci</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>mobile</t>
+  </si>
+  <si>
+    <t>communication email</t>
+  </si>
+  <si>
+    <t>account_email</t>
+  </si>
+  <si>
+    <t>intraday</t>
+  </si>
+  <si>
+    <t>zerodha_access_token</t>
+  </si>
+  <si>
+    <t>current_value</t>
+  </si>
+  <si>
+    <t>bank_fund</t>
+  </si>
+  <si>
+    <t>ipo_blocked_fund</t>
+  </si>
+  <si>
+    <t>holdings_total_value</t>
+  </si>
+  <si>
+    <t>broker_withdrawable_fund</t>
+  </si>
+  <si>
+    <t>broker_investable_fund</t>
+  </si>
+  <si>
+    <t>still_needed_amount</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,83 +100,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,130 +417,88 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AE3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="11.88671875" customWidth="1" min="9" max="9"/>
-    <col width="10.21875" customWidth="1" min="10" max="10"/>
-    <col width="16.21875" customWidth="1" min="11" max="11"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="43.2" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mobile</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>communication email</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>account_email</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>intraday</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>zerodha_access_token</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>current_value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>bank_fund</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ipo_blocked_fund</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>holdings_total_value</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>broker_withdrawable_fund</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>broker_investable_fund</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>still_needed_amount</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
-      <c r="AA1" s="1" t="n"/>
-      <c r="AB1" s="1" t="n"/>
-      <c r="AC1" s="1" t="n"/>
-      <c r="AD1" s="1" t="n"/>
-      <c r="AE1" s="1" t="n"/>
+    <row r="1" spans="1:31" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>90</v>
-      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -1,87 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CFrepo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>uci</t>
-  </si>
-  <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>mobile</t>
-  </si>
-  <si>
-    <t>communication email</t>
-  </si>
-  <si>
-    <t>account_email</t>
-  </si>
-  <si>
-    <t>intraday</t>
-  </si>
-  <si>
-    <t>zerodha_access_token</t>
-  </si>
-  <si>
-    <t>current_value</t>
-  </si>
-  <si>
-    <t>bank_fund</t>
-  </si>
-  <si>
-    <t>ipo_blocked_fund</t>
-  </si>
-  <si>
-    <t>holdings_total_value</t>
-  </si>
-  <si>
-    <t>broker_withdrawable_fund</t>
-  </si>
-  <si>
-    <t>broker_investable_fund</t>
-  </si>
-  <si>
-    <t>still_needed_amount</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -100,24 +46,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -417,86 +422,166 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col width="11.85546875" customWidth="1" min="9" max="9"/>
+    <col width="10.28515625" customWidth="1" min="10" max="10"/>
+    <col width="16.28515625" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="43.15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>communication email</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>account_email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>intraday</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>zerodha_access_token</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bank_fund</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ipo_blocked_fund</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>holdings_total_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>broker_withdrawable_fund</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>broker_investable_fund</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>still_needed_amount</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+      <c r="AE1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Prakhar</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>prakharvasishtha9@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>tok_123</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sonam</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sonampvasishtha@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>tok_456</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>180000</v>
       </c>
     </row>
   </sheetData>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -555,6 +555,9 @@
       <c r="I2" t="n">
         <v>250000</v>
       </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -582,6 +585,9 @@
       </c>
       <c r="I3" t="n">
         <v>180000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>209000</v>
       </c>
     </row>
   </sheetData>
